--- a/AAII_Financials/Yearly/PGR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PGR_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>PGR</t>
   </si>
@@ -656,195 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>62082300</v>
+      </c>
+      <c r="E8" s="3">
         <v>49586400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>47676500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>42638100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>38997700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>31954700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26816100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23417400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>20831900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>19377300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>18156400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17068500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15761100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>56561200</v>
+      </c>
+      <c r="E9" s="3">
         <v>47899300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>42995100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>33965000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>33468800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28490500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>24413600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21715400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>18705900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>17297300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>16275100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>15590900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>14122000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5521100</v>
+      </c>
+      <c r="E10" s="3">
         <v>1687100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4681400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>8673100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>5528900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3464200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2402500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1702000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2126000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2080000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1881300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1477600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1639100</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,51 +961,57 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>224800</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>56910200</v>
+      </c>
+      <c r="E17" s="3">
         <v>48420800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>43247900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>35247900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>33647700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>28624600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>24524100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>21805800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>18784300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17353000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>16318200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15627000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14141400</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>5172100</v>
+      </c>
+      <c r="E18" s="3">
         <v>1165600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>4428600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7390200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5350000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3330100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2292000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1611600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2047600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2024300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1838200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1441500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1619700</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,8 +1179,9 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1187,177 +1221,192 @@
       <c r="O20" s="3">
         <v>0</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>5471800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1502200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4766000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7722000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5656100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>3592500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2528100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1811100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2198100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2121400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1939500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1535900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1708200</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>268400</v>
+      </c>
+      <c r="E22" s="3">
         <v>243500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>218600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>217000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>189700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>166500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>153100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>140900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>136000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>116900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>118200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>123800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>132700</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4903700</v>
+      </c>
+      <c r="E23" s="3">
         <v>922100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4210000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>7173200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>5160300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3163600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2138900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1470700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1911600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1907400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1720000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1317700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1487000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1001300</v>
+      </c>
+      <c r="E24" s="3">
         <v>200600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>859100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1468600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1180300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>542600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>640300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>413500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>611100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>626400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>554600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>415400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>471500</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>3902400</v>
+      </c>
+      <c r="E26" s="3">
         <v>721500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3350900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>5704600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3980000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2621000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1498600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1057200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1300500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1281000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1165400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>902300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1015500</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3864800</v>
+      </c>
+      <c r="E27" s="3">
         <v>694600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3324000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>5677700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3943400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2593900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1492700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1031000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1267600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1281000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1165400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>902300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1015500</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1581,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,12 +1605,12 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3">
         <v>99500</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
@@ -1565,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,9 +1716,12 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1691,51 +1761,57 @@
       <c r="O32" s="3">
         <v>0</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3864800</v>
+      </c>
+      <c r="E33" s="3">
         <v>694600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3324000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>5677700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3943400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2593900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1592200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1031000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1267600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1281000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1165400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>902300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1015500</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3864800</v>
+      </c>
+      <c r="E35" s="3">
         <v>694600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3324000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>5677700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3943400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2593900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1592200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1031000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1267600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1281000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1165400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>902300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1015500</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>84900</v>
+      </c>
+      <c r="E41" s="3">
         <v>203500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>187100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>76500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>226200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>265000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>211500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>224400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>108400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>75100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>179100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>155700</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1984,51 +2074,57 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>11958200</v>
+      </c>
+      <c r="E43" s="3">
         <v>10416900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>9399500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>8160100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7507300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6497100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5422500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4509200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3987700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3537500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3310700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3293100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3125800</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2164,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2105,14 +2204,17 @@
         <v>0</v>
       </c>
       <c r="N45" s="3">
+        <v>0</v>
+      </c>
+      <c r="O45" s="3">
         <v>66300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>69800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,135 +2254,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>65998600</v>
+      </c>
+      <c r="E47" s="3">
         <v>53548300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>51514100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>47530300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>39254300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>33567400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>27274700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>23482600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>20937300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>19018000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>18054700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>16475500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>15963000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1053300</v>
+      </c>
+      <c r="E48" s="3">
         <v>1164500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1309900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1271500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1401900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1131700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1119600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1177100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1037200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1921200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>960900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>933700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>911300</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>227900</v>
+      </c>
+      <c r="E49" s="3">
         <v>314200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>570000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>624100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>681000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>747300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>819300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>882200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>942500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>12900</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,36 +2479,39 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>950700</v>
+      </c>
+      <c r="E52" s="3">
         <v>1148900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15000</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
         <v>1200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>48700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14900</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2404,9 +2524,12 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>88690800</v>
+      </c>
+      <c r="E54" s="3">
         <v>75465000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>71132300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>64098300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>54910500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>46575000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>38701200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>33427500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>29819300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>25787600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>24408200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>22694700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>21844800</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,50 +2655,54 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6825000</v>
+      </c>
+      <c r="E57" s="3">
         <v>5395600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>5829700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4776800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>4415500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5046500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2825900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2495500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2067800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1893800</v>
       </c>
-      <c r="M57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2579,80 +2713,86 @@
         <v>0</v>
       </c>
       <c r="F58" s="3">
+        <v>0</v>
+      </c>
+      <c r="G58" s="3">
         <v>499800</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
         <v>0</v>
       </c>
       <c r="I58" s="3">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>25000</v>
       </c>
       <c r="K58" s="3">
+        <v>25000</v>
+      </c>
+      <c r="L58" s="3">
         <v>27200</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>8</v>
+      <c r="M58" s="3">
+        <v>0</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20310900</v>
+      </c>
+      <c r="E59" s="3">
         <v>17430800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>15855200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16311000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13965700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10686500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9558600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7863700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7141000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5844200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7849700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6786200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6350200</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,93 +2832,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>6888600</v>
+      </c>
+      <c r="E61" s="3">
         <v>6388300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4898800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4896300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4407100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4404900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3281300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3123200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2680700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2164700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1860900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2063100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2442100</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>0</v>
+      <c r="D62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E62" s="3">
+        <v>0</v>
+      </c>
+      <c r="F62" s="3">
         <v>152900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>310000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>118000</v>
       </c>
-      <c r="H62" s="3">
-        <v>0</v>
-      </c>
       <c r="I62" s="3">
+        <v>0</v>
+      </c>
+      <c r="J62" s="3">
         <v>135000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>111300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>109300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>98900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>28400</v>
       </c>
-      <c r="N62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>68413700</v>
+      </c>
+      <c r="E66" s="3">
         <v>59574000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>52900700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>47059700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>41237300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>35753200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>29416400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>25470400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>22529900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>18859000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18218700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>16687700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16038100</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3062,14 +3230,14 @@
         <v>493900</v>
       </c>
       <c r="G70" s="3">
+        <v>493900</v>
+      </c>
+      <c r="H70" s="3">
         <v>987800</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>493900</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -3088,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>18800500</v>
+      </c>
+      <c r="E72" s="3">
         <v>15721200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>15339700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>13354900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10679600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8386600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6031700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>5140400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>4686600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4133400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3500000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3454400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3495000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>19783200</v>
+      </c>
+      <c r="E76" s="3">
         <v>15397100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17737700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16544700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>12685400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>10327900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9284800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7957100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7289400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6928600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6189500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6007000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5806700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3864800</v>
+      </c>
+      <c r="E81" s="3">
         <v>694600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3324000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>5677700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3943400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2593900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1592200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1031000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1267600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1281000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1165400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>902300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1015500</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>299700</v>
+      </c>
+      <c r="E83" s="3">
         <v>336600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>337400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>331800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>306100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>262400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>236100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>199500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>150500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>97100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>101300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>94400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>88500</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>10643300</v>
+      </c>
+      <c r="E89" s="3">
         <v>6848800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>7761700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6905600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6261600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6284800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>3756800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2732700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2292900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1725600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1899900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1691400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1497900</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-252000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-292000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-243500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-223500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-363500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-266000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-155700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-215000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-130700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-108100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-140400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-127700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10842600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-7956200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-3119800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6117700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4338300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7034900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3406700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2480700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1923900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-836900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1356500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-264900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-744900</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-277600</v>
+      </c>
+      <c r="E96" s="3">
         <v>-260800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3773300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-1577800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-1670000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-668400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-395400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-519000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-403600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-892600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-175600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-853700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-263600</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,51 +4398,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>78000</v>
+      </c>
+      <c r="E100" s="3">
         <v>1126200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4516300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-938800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1770900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>549800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-300900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-250400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-252800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-855400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-646800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1404100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-755700</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4212,76 +4461,82 @@
       <c r="F101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G101" s="3">
-        <v>0</v>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H101" s="3">
         <v>0</v>
       </c>
       <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3">
         <v>-300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-121300</v>
+      </c>
+      <c r="E102" s="3">
         <v>18800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>125600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-150900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>152400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-200300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>48900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>116000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>33300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-104000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-3200</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PGR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PGR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>PGR</t>
   </si>
@@ -970,8 +970,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
         <v>224800</v>
@@ -982,14 +982,14 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>1000</v>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>-1600</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>299700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>336600</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>337400</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>331800</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>306100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>262400</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>236100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1080,7 +1080,7 @@
         <v>56910200</v>
       </c>
       <c r="E17" s="3">
-        <v>48420800</v>
+        <v>48196000</v>
       </c>
       <c r="F17" s="3">
         <v>43247900</v>
@@ -1095,7 +1095,7 @@
         <v>28624600</v>
       </c>
       <c r="J17" s="3">
-        <v>24524100</v>
+        <v>24523100</v>
       </c>
       <c r="K17" s="3">
         <v>21805800</v>
@@ -1125,7 +1125,7 @@
         <v>5172100</v>
       </c>
       <c r="E18" s="3">
-        <v>1165600</v>
+        <v>1390400</v>
       </c>
       <c r="F18" s="3">
         <v>4428600</v>
@@ -1140,7 +1140,7 @@
         <v>3330100</v>
       </c>
       <c r="J18" s="3">
-        <v>2292000</v>
+        <v>2293000</v>
       </c>
       <c r="K18" s="3">
         <v>1611600</v>
@@ -1185,26 +1185,26 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>0</v>
-      </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>0</v>
-      </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
-      <c r="I20" s="3">
-        <v>0</v>
+      <c r="D20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J20" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>5471800</v>
       </c>
       <c r="E21" s="3">
-        <v>1502200</v>
+        <v>1727000</v>
       </c>
       <c r="F21" s="3">
         <v>4766000</v>
@@ -1384,7 +1384,7 @@
         <v>542600</v>
       </c>
       <c r="J24" s="3">
-        <v>640300</v>
+        <v>540800</v>
       </c>
       <c r="K24" s="3">
         <v>413500</v>
@@ -1474,7 +1474,7 @@
         <v>2621000</v>
       </c>
       <c r="J26" s="3">
-        <v>1498600</v>
+        <v>1598100</v>
       </c>
       <c r="K26" s="3">
         <v>1057200</v>
@@ -1519,7 +1519,7 @@
         <v>2593900</v>
       </c>
       <c r="J27" s="3">
-        <v>1492700</v>
+        <v>1592200</v>
       </c>
       <c r="K27" s="3">
         <v>1031000</v>
@@ -1590,26 +1590,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>99500</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,26 +1725,26 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>0</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0</v>
+      <c r="D32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J32" s="3">
-        <v>0</v>
+        <v>-1000</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1771,22 +1771,22 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3864800</v>
+        <v>3902400</v>
       </c>
       <c r="E33" s="3">
-        <v>694600</v>
+        <v>721500</v>
       </c>
       <c r="F33" s="3">
-        <v>3324000</v>
+        <v>3350900</v>
       </c>
       <c r="G33" s="3">
-        <v>5677700</v>
+        <v>5704600</v>
       </c>
       <c r="H33" s="3">
-        <v>3943400</v>
+        <v>3970300</v>
       </c>
       <c r="I33" s="3">
-        <v>2593900</v>
+        <v>2615300</v>
       </c>
       <c r="J33" s="3">
         <v>1592200</v>
@@ -1861,22 +1861,22 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3864800</v>
+        <v>3902400</v>
       </c>
       <c r="E35" s="3">
-        <v>694600</v>
+        <v>721500</v>
       </c>
       <c r="F35" s="3">
-        <v>3324000</v>
+        <v>3350900</v>
       </c>
       <c r="G35" s="3">
-        <v>5677700</v>
+        <v>5704600</v>
       </c>
       <c r="H35" s="3">
-        <v>3943400</v>
+        <v>3970300</v>
       </c>
       <c r="I35" s="3">
-        <v>2593900</v>
+        <v>2615300</v>
       </c>
       <c r="J35" s="3">
         <v>1592200</v>
@@ -2039,25 +2039,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>1789900</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>2861700</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>942600</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>5218500</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>1798800</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>1795900</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>2869400</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2090,7 +2090,7 @@
         <v>10416900</v>
       </c>
       <c r="F43" s="3">
-        <v>9399500</v>
+        <v>9960200</v>
       </c>
       <c r="G43" s="3">
         <v>8160100</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>5609100</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>6163300</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>5173000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>4252400</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>3593100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>2926200</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>2398400</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2219,25 +2219,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>19706600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>19958300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>16735500</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>18075600</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>13753100</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>11603900</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>11168900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2264,25 +2264,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>65998600</v>
+        <v>64208700</v>
       </c>
       <c r="E47" s="3">
-        <v>53548300</v>
+        <v>50686600</v>
       </c>
       <c r="F47" s="3">
-        <v>51514100</v>
+        <v>50571500</v>
       </c>
       <c r="G47" s="3">
-        <v>47530300</v>
+        <v>42311800</v>
       </c>
       <c r="H47" s="3">
-        <v>39254300</v>
+        <v>37455500</v>
       </c>
       <c r="I47" s="3">
-        <v>33567400</v>
+        <v>31771500</v>
       </c>
       <c r="J47" s="3">
-        <v>27274700</v>
+        <v>24405300</v>
       </c>
       <c r="K47" s="3">
         <v>23482600</v>
@@ -2354,25 +2354,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>227900</v>
+        <v>1915300</v>
       </c>
       <c r="E49" s="3">
-        <v>314200</v>
+        <v>1772300</v>
       </c>
       <c r="F49" s="3">
-        <v>570000</v>
+        <v>1925600</v>
       </c>
       <c r="G49" s="3">
-        <v>624100</v>
+        <v>1861300</v>
       </c>
       <c r="H49" s="3">
-        <v>681000</v>
+        <v>1737500</v>
       </c>
       <c r="I49" s="3">
-        <v>747300</v>
+        <v>1698900</v>
       </c>
       <c r="J49" s="3">
-        <v>819300</v>
+        <v>1599800</v>
       </c>
       <c r="K49" s="3">
         <v>882200</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>950700</v>
+        <v>742900</v>
       </c>
       <c r="E52" s="3">
-        <v>1148900</v>
+        <v>646200</v>
       </c>
       <c r="F52" s="3">
-        <v>15000</v>
+        <v>525800</v>
       </c>
       <c r="G52" s="3">
-        <v>0</v>
+        <v>540900</v>
       </c>
       <c r="H52" s="3">
-        <v>1200</v>
+        <v>547300</v>
       </c>
       <c r="I52" s="3">
-        <v>48700</v>
+        <v>325800</v>
       </c>
       <c r="J52" s="3">
-        <v>10300</v>
+        <v>407600</v>
       </c>
       <c r="K52" s="3">
         <v>14900</v>
@@ -2662,25 +2662,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>6825000</v>
+        <v>40902400</v>
       </c>
       <c r="E57" s="3">
-        <v>5395600</v>
+        <v>35881200</v>
       </c>
       <c r="F57" s="3">
-        <v>5829700</v>
+        <v>31907400</v>
       </c>
       <c r="G57" s="3">
-        <v>4776800</v>
+        <v>24779600</v>
       </c>
       <c r="H57" s="3">
-        <v>4415500</v>
+        <v>22283800</v>
       </c>
       <c r="I57" s="3">
-        <v>5046500</v>
+        <v>18956700</v>
       </c>
       <c r="J57" s="3">
-        <v>2825900</v>
+        <v>15889000</v>
       </c>
       <c r="K57" s="3">
         <v>2495500</v>
@@ -2707,7 +2707,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>74000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2716,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="G58" s="3">
-        <v>499800</v>
+        <v>0</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2725,7 +2725,7 @@
         <v>0</v>
       </c>
       <c r="J58" s="3">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3">
         <v>25000</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20310900</v>
+        <v>20445500</v>
       </c>
       <c r="E59" s="3">
-        <v>17430800</v>
+        <v>17304500</v>
       </c>
       <c r="F59" s="3">
-        <v>15855200</v>
+        <v>15615800</v>
       </c>
       <c r="G59" s="3">
-        <v>16311000</v>
+        <v>16295500</v>
       </c>
       <c r="H59" s="3">
-        <v>13965700</v>
+        <v>13988200</v>
       </c>
       <c r="I59" s="3">
-        <v>10686500</v>
+        <v>12171200</v>
       </c>
       <c r="J59" s="3">
-        <v>9558600</v>
+        <v>9582400</v>
       </c>
       <c r="K59" s="3">
         <v>7863700</v>
@@ -2797,25 +2797,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>61421900</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>53185700</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>47523200</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>41075100</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>36272000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>31127900</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>25471400</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2842,25 +2842,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6888600</v>
+        <v>6991800</v>
       </c>
       <c r="E61" s="3">
         <v>6388300</v>
       </c>
       <c r="F61" s="3">
-        <v>4898800</v>
+        <v>5079700</v>
       </c>
       <c r="G61" s="3">
-        <v>4896300</v>
+        <v>5575100</v>
       </c>
       <c r="H61" s="3">
-        <v>4407100</v>
+        <v>4608600</v>
       </c>
       <c r="I61" s="3">
         <v>4404900</v>
       </c>
       <c r="J61" s="3">
-        <v>3281300</v>
+        <v>3306300</v>
       </c>
       <c r="K61" s="3">
         <v>3123200</v>
@@ -2889,23 +2889,23 @@
       <c r="D62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E62" s="3">
-        <v>0</v>
+      <c r="E62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F62" s="3">
-        <v>152900</v>
+        <v>143400</v>
       </c>
       <c r="G62" s="3">
-        <v>310000</v>
+        <v>95500</v>
       </c>
       <c r="H62" s="3">
-        <v>118000</v>
+        <v>11900</v>
       </c>
       <c r="I62" s="3">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3">
-        <v>135000</v>
+        <v>5900</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K62" s="3">
         <v>111300</v>
@@ -3079,13 +3079,13 @@
         <v>47059700</v>
       </c>
       <c r="H66" s="3">
-        <v>41237300</v>
+        <v>41011700</v>
       </c>
       <c r="I66" s="3">
-        <v>35753200</v>
+        <v>35538700</v>
       </c>
       <c r="J66" s="3">
-        <v>29416400</v>
+        <v>28912700</v>
       </c>
       <c r="K66" s="3">
         <v>25470400</v>
@@ -3233,7 +3233,7 @@
         <v>493900</v>
       </c>
       <c r="H70" s="3">
-        <v>987800</v>
+        <v>493900</v>
       </c>
       <c r="I70" s="3">
         <v>493900</v>
@@ -3503,7 +3503,7 @@
         <v>16544700</v>
       </c>
       <c r="H76" s="3">
-        <v>12685400</v>
+        <v>13179300</v>
       </c>
       <c r="I76" s="3">
         <v>10327900</v>
@@ -3631,22 +3631,22 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3864800</v>
+        <v>3902400</v>
       </c>
       <c r="E81" s="3">
-        <v>694600</v>
+        <v>721500</v>
       </c>
       <c r="F81" s="3">
-        <v>3324000</v>
+        <v>3350900</v>
       </c>
       <c r="G81" s="3">
-        <v>5677700</v>
+        <v>5704600</v>
       </c>
       <c r="H81" s="3">
-        <v>3943400</v>
+        <v>3970300</v>
       </c>
       <c r="I81" s="3">
-        <v>2593900</v>
+        <v>2615300</v>
       </c>
       <c r="J81" s="3">
         <v>1592200</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>299700</v>
+        <v>285500</v>
       </c>
       <c r="E83" s="3">
-        <v>336600</v>
+        <v>305600</v>
       </c>
       <c r="F83" s="3">
-        <v>337400</v>
+        <v>279700</v>
       </c>
       <c r="G83" s="3">
-        <v>331800</v>
+        <v>274900</v>
       </c>
       <c r="H83" s="3">
-        <v>306100</v>
+        <v>239800</v>
       </c>
       <c r="I83" s="3">
-        <v>262400</v>
+        <v>190400</v>
       </c>
       <c r="J83" s="3">
-        <v>236100</v>
+        <v>169900</v>
       </c>
       <c r="K83" s="3">
         <v>199500</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-277600</v>
+        <v>234000</v>
       </c>
       <c r="E96" s="3">
-        <v>-260800</v>
+        <v>234000</v>
       </c>
       <c r="F96" s="3">
-        <v>-3773300</v>
+        <v>3746500</v>
       </c>
       <c r="G96" s="3">
-        <v>-1577800</v>
+        <v>1551000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1670000</v>
+        <v>1643200</v>
       </c>
       <c r="I96" s="3">
-        <v>-668400</v>
+        <v>654900</v>
       </c>
       <c r="J96" s="3">
-        <v>-395400</v>
+        <v>395400</v>
       </c>
       <c r="K96" s="3">
         <v>-519000</v>
@@ -4464,11 +4464,11 @@
       <c r="G101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J101" s="3">
         <v>-300</v>

--- a/AAII_Financials/Yearly/PGR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PGR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
   <si>
     <t>PGR</t>
   </si>
@@ -656,208 +656,221 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>62082300</v>
+        <v>75343000</v>
       </c>
       <c r="E8" s="3">
-        <v>49586400</v>
+        <v>62083000</v>
       </c>
       <c r="F8" s="3">
+        <v>49587000</v>
+      </c>
+      <c r="G8" s="3">
         <v>47676500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>42638100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>38997700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>31954700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>26816100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23417400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>20831900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>19377300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>18156400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17068500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15761100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>56561200</v>
+        <v>63905000</v>
       </c>
       <c r="E9" s="3">
-        <v>47899300</v>
+        <v>56562000</v>
       </c>
       <c r="F9" s="3">
+        <v>47899000</v>
+      </c>
+      <c r="G9" s="3">
         <v>42995100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>33965000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>33468800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>28490500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>24413600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21715400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>18705900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>17297300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16275100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>15590900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>14122000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>5521100</v>
+        <v>11438000</v>
       </c>
       <c r="E10" s="3">
-        <v>1687100</v>
+        <v>5521000</v>
       </c>
       <c r="F10" s="3">
+        <v>1688000</v>
+      </c>
+      <c r="G10" s="3">
         <v>4681400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>8673100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>5528900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3464200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2402500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1702000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2126000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2080000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1881300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1477600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1639100</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,8 +888,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,9 +933,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,20 +981,23 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E14" s="3">
-        <v>224800</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="3">
+        <v>225000</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>8</v>
@@ -991,54 +1011,57 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3">
         <v>-1600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>299700</v>
+        <v>284000</v>
       </c>
       <c r="E15" s="3">
-        <v>336600</v>
+        <v>285000</v>
       </c>
       <c r="F15" s="3">
+        <v>306000</v>
+      </c>
+      <c r="G15" s="3">
         <v>337400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>331800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>306100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>262400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>236100</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1077,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1097,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>56910200</v>
+        <v>64351000</v>
       </c>
       <c r="E17" s="3">
+        <v>56911000</v>
+      </c>
+      <c r="F17" s="3">
         <v>48196000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>43247900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>35247900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>33647700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>28624600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>24523100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>21805800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>18784300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17353000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>16318200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15627000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>14141400</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5172100</v>
+        <v>10992000</v>
       </c>
       <c r="E18" s="3">
-        <v>1390400</v>
+        <v>5172000</v>
       </c>
       <c r="F18" s="3">
+        <v>1391000</v>
+      </c>
+      <c r="G18" s="3">
         <v>4428600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>7390200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5350000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>3330100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2293000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1611600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>2047600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2024300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1838200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1441500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1619700</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,8 +1213,9 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1203,12 +1237,12 @@
       <c r="I20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J20" s="3">
+      <c r="J20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K20" s="3">
         <v>1000</v>
       </c>
-      <c r="K20" s="3">
-        <v>0</v>
-      </c>
       <c r="L20" s="3">
         <v>0</v>
       </c>
@@ -1224,189 +1258,204 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>5471800</v>
+        <v>11276000</v>
       </c>
       <c r="E21" s="3">
-        <v>1727000</v>
+        <v>5457000</v>
       </c>
       <c r="F21" s="3">
+        <v>1697000</v>
+      </c>
+      <c r="G21" s="3">
         <v>4766000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>7722000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>5656100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>3592500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2528100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1811100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>2198100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2121400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1939500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1535900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1708200</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>268400</v>
+        <v>279000</v>
       </c>
       <c r="E22" s="3">
-        <v>243500</v>
+        <v>268000</v>
       </c>
       <c r="F22" s="3">
+        <v>244000</v>
+      </c>
+      <c r="G22" s="3">
         <v>218600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>217000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>189700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>166500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>153100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>140900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>136000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>116900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>118200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>123800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>132700</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>4903700</v>
+        <v>10713000</v>
       </c>
       <c r="E23" s="3">
-        <v>922100</v>
+        <v>4904000</v>
       </c>
       <c r="F23" s="3">
+        <v>922000</v>
+      </c>
+      <c r="G23" s="3">
         <v>4210000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>7173200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5160300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3163600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2138900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1470700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1911600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1907400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1720000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1317700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1487000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1001300</v>
+        <v>2233000</v>
       </c>
       <c r="E24" s="3">
-        <v>200600</v>
+        <v>1001000</v>
       </c>
       <c r="F24" s="3">
+        <v>200000</v>
+      </c>
+      <c r="G24" s="3">
         <v>859100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1468600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1180300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>542600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>540800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>413500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>611100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>626400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>554600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>415400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>471500</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1498,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>3902400</v>
+        <v>8480000</v>
       </c>
       <c r="E26" s="3">
-        <v>721500</v>
+        <v>3903000</v>
       </c>
       <c r="F26" s="3">
+        <v>722000</v>
+      </c>
+      <c r="G26" s="3">
         <v>3350900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>5704600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3980000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2621000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1598100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1057200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1300500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1281000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1165400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>902300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1015500</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3864800</v>
+        <v>8463000</v>
       </c>
       <c r="E27" s="3">
-        <v>694600</v>
+        <v>3865000</v>
       </c>
       <c r="F27" s="3">
+        <v>695000</v>
+      </c>
+      <c r="G27" s="3">
         <v>3324000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>5677700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3943400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2593900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1592200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1031000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1267600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1281000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1165400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>902300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1015500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1642,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1672,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1629,9 +1690,12 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1738,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,9 +1786,12 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1743,12 +1813,12 @@
       <c r="I32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J32" s="3">
+      <c r="J32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K32" s="3">
         <v>-1000</v>
       </c>
-      <c r="K32" s="3">
-        <v>0</v>
-      </c>
       <c r="L32" s="3">
         <v>0</v>
       </c>
@@ -1764,54 +1834,60 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3902400</v>
+        <v>8480000</v>
       </c>
       <c r="E33" s="3">
-        <v>721500</v>
+        <v>3903000</v>
       </c>
       <c r="F33" s="3">
+        <v>722000</v>
+      </c>
+      <c r="G33" s="3">
         <v>3350900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>5704600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3970300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2615300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1592200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1031000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1267600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1281000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1165400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>902300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1015500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1930,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3902400</v>
+        <v>8480000</v>
       </c>
       <c r="E35" s="3">
-        <v>721500</v>
+        <v>3903000</v>
       </c>
       <c r="F35" s="3">
+        <v>722000</v>
+      </c>
+      <c r="G35" s="3">
         <v>3350900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>5704600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3970300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2615300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1592200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1031000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1267600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1281000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1165400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>902300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1015500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2054,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,80 +2074,84 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>84900</v>
+        <v>143000</v>
       </c>
       <c r="E41" s="3">
+        <v>85000</v>
+      </c>
+      <c r="F41" s="3">
         <v>203500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>187100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>76500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>226200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>69500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>265000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>211500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>224400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>108400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>75100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>179100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>155700</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>1789900</v>
+        <v>615000</v>
       </c>
       <c r="E42" s="3">
+        <v>1790000</v>
+      </c>
+      <c r="F42" s="3">
         <v>2861700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>942600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5218500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1798800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1795900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>2869400</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2077,54 +2167,60 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>11958200</v>
+        <v>14369000</v>
       </c>
       <c r="E43" s="3">
+        <v>11958000</v>
+      </c>
+      <c r="F43" s="3">
         <v>10416900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>9960200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8160100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7507300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6497100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5422500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>4509200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3987700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3537500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3310700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3293100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3125800</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2149,8 +2245,8 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2167,36 +2263,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5609100</v>
+        <v>5488000</v>
       </c>
       <c r="E45" s="3">
+        <v>5609000</v>
+      </c>
+      <c r="F45" s="3">
         <v>6163300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5173000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4252400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3593100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2926200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2398400</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2207,41 +2306,44 @@
         <v>0</v>
       </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>66300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>69800</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>19706600</v>
+        <v>20975000</v>
       </c>
       <c r="E46" s="3">
+        <v>19707000</v>
+      </c>
+      <c r="F46" s="3">
         <v>19958300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>16735500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>18075600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>13753100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>11603900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11168900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2257,144 +2359,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>64208700</v>
+        <v>79635000</v>
       </c>
       <c r="E47" s="3">
+        <v>64209000</v>
+      </c>
+      <c r="F47" s="3">
         <v>50686600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>50571500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>42311800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>37455500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>31771500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>24405300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>23482600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>20937300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>19018000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>18054700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>16475500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>15963000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1053300</v>
+        <v>983000</v>
       </c>
       <c r="E48" s="3">
+        <v>1054000</v>
+      </c>
+      <c r="F48" s="3">
         <v>1164500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1309900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1271500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1401900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1131700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1119600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1177100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1037200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1921200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>960900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>933700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>911300</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1915300</v>
+        <v>2189000</v>
       </c>
       <c r="E49" s="3">
+        <v>1915000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1772300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1925600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1861300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1737500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1698900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1599800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>882200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>942500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>12900</v>
       </c>
-      <c r="N49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2551,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,39 +2599,42 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>742900</v>
+        <v>846000</v>
       </c>
       <c r="E52" s="3">
+        <v>742000</v>
+      </c>
+      <c r="F52" s="3">
         <v>646200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>525800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>540900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>547300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>325800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>407600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14900</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="M52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2527,9 +2647,12 @@
       <c r="P52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2695,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>88690800</v>
+        <v>105745000</v>
       </c>
       <c r="E54" s="3">
+        <v>88691000</v>
+      </c>
+      <c r="F54" s="3">
         <v>75465000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>71132300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>64098300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>54910500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>46575000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>38701200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>33427500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>29819300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>25787600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>24408200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>22694700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>21844800</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2766,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,58 +2786,62 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>40902400</v>
+        <v>49181000</v>
       </c>
       <c r="E57" s="3">
+        <v>40902000</v>
+      </c>
+      <c r="F57" s="3">
         <v>35881200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31907400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24779600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>22283800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>18956700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15889000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2495500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2067800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1893800</v>
       </c>
-      <c r="N57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>74000</v>
+        <v>81000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2728,98 +2862,104 @@
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>25000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>27200</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>20445500</v>
+        <v>23884000</v>
       </c>
       <c r="E59" s="3">
+        <v>20446000</v>
+      </c>
+      <c r="F59" s="3">
         <v>17304500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>15615800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16295500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13988200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12171200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9582400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7863700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7141000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5844200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7849700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6786200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6350200</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>61421900</v>
+        <v>73146000</v>
       </c>
       <c r="E60" s="3">
+        <v>61348000</v>
+      </c>
+      <c r="F60" s="3">
         <v>53185700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>47523200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>41075100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>36272000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>31127900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>25471400</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -2835,54 +2975,60 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>6991800</v>
+        <v>7008000</v>
       </c>
       <c r="E61" s="3">
+        <v>7066000</v>
+      </c>
+      <c r="F61" s="3">
         <v>6388300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>5079700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5575100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4608600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4404900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3306300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3123200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2680700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2164700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1860900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2063100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2442100</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -2892,42 +3038,45 @@
       <c r="E62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F62" s="3">
+      <c r="F62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G62" s="3">
         <v>143400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>95500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5900</v>
       </c>
-      <c r="J62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L62" s="3">
         <v>111300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>109300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>98900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>28400</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3119,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3167,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3215,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>68413700</v>
+        <v>80154000</v>
       </c>
       <c r="E66" s="3">
+        <v>68414000</v>
+      </c>
+      <c r="F66" s="3">
         <v>59574000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>52900700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>47059700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>41011700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>35538700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>28912700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>25470400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>22529900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>18859000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18218700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>16687700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16038100</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3286,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3331,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,17 +3379,20 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>493900</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>493900</v>
+        <v>494000</v>
       </c>
       <c r="F70" s="3">
         <v>493900</v>
@@ -3239,7 +3407,7 @@
         <v>493900</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>493900</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3259,9 +3427,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3475,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>18800500</v>
+        <v>24283000</v>
       </c>
       <c r="E72" s="3">
+        <v>18801000</v>
+      </c>
+      <c r="F72" s="3">
         <v>15721200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15339700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>13354900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10679600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8386600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6031700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5140400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>4686600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4133400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3500000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3454400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3495000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3571,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3619,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3667,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>19783200</v>
+        <v>25591000</v>
       </c>
       <c r="E76" s="3">
+        <v>19783000</v>
+      </c>
+      <c r="F76" s="3">
         <v>15397100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>17737700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16544700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>13179300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>10327900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>9284800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7957100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7289400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6928600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6189500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6007000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5806700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3763,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3902400</v>
+        <v>8480000</v>
       </c>
       <c r="E81" s="3">
-        <v>721500</v>
+        <v>3903000</v>
       </c>
       <c r="F81" s="3">
+        <v>722000</v>
+      </c>
+      <c r="G81" s="3">
         <v>3350900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>5704600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3970300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2615300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1592200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1031000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1267600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1281000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1165400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>902300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1015500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3887,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>285500</v>
+        <v>284000</v>
       </c>
       <c r="E83" s="3">
-        <v>305600</v>
+        <v>285000</v>
       </c>
       <c r="F83" s="3">
+        <v>306000</v>
+      </c>
+      <c r="G83" s="3">
         <v>279700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>274900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>239800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>190400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>169900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>199500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>150500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>97100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>101300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>94400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>88500</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3980,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4028,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4076,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4124,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4172,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>10643300</v>
+        <v>15119000</v>
       </c>
       <c r="E89" s="3">
-        <v>6848800</v>
+        <v>10643000</v>
       </c>
       <c r="F89" s="3">
+        <v>6849000</v>
+      </c>
+      <c r="G89" s="3">
         <v>7761700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>6905600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6261600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6284800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>3756800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2732700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2292900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1725600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1899900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1691400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1497900</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4243,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-285000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-252000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-292000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-243500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-223500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-363500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-266000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-155700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-215000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-130700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-108100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-140400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-127700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-78900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4336,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4384,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-10842600</v>
+        <v>-13749000</v>
       </c>
       <c r="E94" s="3">
-        <v>-7956200</v>
+        <v>-10842000</v>
       </c>
       <c r="F94" s="3">
+        <v>-7956000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-3119800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6117700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4338300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7034900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3406700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2480700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1923900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-836900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1356500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-264900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-744900</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,53 +4455,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>234000</v>
+        <v>674000</v>
       </c>
       <c r="E96" s="3">
         <v>234000</v>
       </c>
       <c r="F96" s="3">
+        <v>234000</v>
+      </c>
+      <c r="G96" s="3">
         <v>3746500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1551000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1643200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>654900</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>395400</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-519000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-403600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-892600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-175600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-853700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-263600</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4548,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4596,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,54 +4644,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1316000</v>
+      </c>
+      <c r="E100" s="3">
         <v>78000</v>
       </c>
-      <c r="E100" s="3">
-        <v>1126200</v>
-      </c>
       <c r="F100" s="3">
+        <v>1126000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-4516300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-938800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1770900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>549800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-300900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-250400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-252800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-855400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-646800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1404100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-755700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4470,73 +4719,79 @@
       <c r="I101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J101" s="3">
+      <c r="J101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K101" s="3">
         <v>-300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>-600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-500</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-121300</v>
+        <v>54000</v>
       </c>
       <c r="E102" s="3">
-        <v>18800</v>
+        <v>-121000</v>
       </c>
       <c r="F102" s="3">
+        <v>19000</v>
+      </c>
+      <c r="G102" s="3">
         <v>125600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-150900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>152400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-200300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>48900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>116000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>33300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-104000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-3200</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/PGR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/PGR_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>PGR</t>
   </si>
@@ -656,221 +656,233 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>87637000</v>
+      </c>
+      <c r="E8" s="3">
         <v>75343000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>62083000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>49587000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>47676500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>42638100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>38997700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>31954700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>26816100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>23417400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>20831900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>19377300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>18156400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17068500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>15761100</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>71384000</v>
+      </c>
+      <c r="E9" s="3">
         <v>63905000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>56562000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>47899000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>42995100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>33965000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>33468800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28490500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>24413600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21715400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>18705900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>17297300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16275100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>15590900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>14122000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>16253000</v>
+      </c>
+      <c r="E10" s="3">
         <v>11438000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5521000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1688000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>4681400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>8673100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>5528900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3464200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2402500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1702000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2126000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2080000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1881300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1477600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1639100</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -889,8 +901,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -936,9 +949,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -984,9 +1000,12 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -996,12 +1015,12 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>225000</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1014,57 +1033,60 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>-1600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E15" s="3">
         <v>284000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>285000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>306000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>337400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>331800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>306100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>262400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>236100</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1080,9 +1102,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1098,104 +1123,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>73136000</v>
+      </c>
+      <c r="E17" s="3">
         <v>64351000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>56911000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48196000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>43247900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>35247900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>33647700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>28624600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>24523100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>21805800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>18784300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17353000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>16318200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15627000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>14141400</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>14501000</v>
+      </c>
+      <c r="E18" s="3">
         <v>10992000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5172000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1391000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>4428600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>7390200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5350000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>3330100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>2293000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1611600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>2047600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2024300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1838200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1441500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1619700</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,8 +1246,9 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1240,12 +1273,12 @@
       <c r="J20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L20" s="3">
         <v>1000</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1261,201 +1294,216 @@
       <c r="Q20" s="3">
         <v>0</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14814000</v>
+      </c>
+      <c r="E21" s="3">
         <v>11276000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5457000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>1697000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>4766000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>7722000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>5656100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>3592500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2528100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1811100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>2198100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>2121400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1939500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1535900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1708200</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>278000</v>
+      </c>
+      <c r="E22" s="3">
         <v>279000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>268000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>244000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>218600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>217000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>189700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>166500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>153100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>140900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>136000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>116900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>118200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>123800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>132700</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>14223000</v>
+      </c>
+      <c r="E23" s="3">
         <v>10713000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4904000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>922000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4210000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>7173200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>5160300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3163600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>2138900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1470700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1911600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1907400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1720000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1317700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1487000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>2915000</v>
+      </c>
+      <c r="E24" s="3">
         <v>2233000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1001000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>859100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1468600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1180300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>542600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>540800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>413500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>611100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>626400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>554600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>415400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>471500</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1501,105 +1549,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>11308000</v>
+      </c>
+      <c r="E26" s="3">
         <v>8480000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3903000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>722000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3350900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>5704600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3980000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2621000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1598100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1057200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1300500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1281000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1165400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>902300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1015500</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>11308000</v>
+      </c>
+      <c r="E27" s="3">
         <v>8463000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3865000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>695000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3324000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>5677700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3943400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2593900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1592200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1031000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1267600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1281000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1165400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>902300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1015500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1645,9 +1702,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1675,8 +1735,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -1693,9 +1753,12 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1741,9 +1804,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1789,9 +1855,12 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1816,12 +1885,12 @@
       <c r="J32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L32" s="3">
         <v>-1000</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -1837,57 +1906,63 @@
       <c r="Q32" s="3">
         <v>0</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>11308000</v>
+      </c>
+      <c r="E33" s="3">
         <v>8480000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3903000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>722000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3350900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>5704600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3970300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2615300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1592200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1031000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1267600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1281000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1165400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>902300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1015500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1933,110 +2008,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>11308000</v>
+      </c>
+      <c r="E35" s="3">
         <v>8480000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3903000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>722000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3350900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>5704600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3970300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2615300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1592200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1031000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1267600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1281000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1165400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>902300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1015500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2055,8 +2139,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2075,86 +2160,90 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>125000</v>
+      </c>
+      <c r="E41" s="3">
         <v>143000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>85000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>203500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>187100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>76500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>226200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>69500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>265000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>211500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>224400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>108400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>75100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>179100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>155700</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>10005000</v>
+      </c>
+      <c r="E42" s="3">
         <v>615000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>1790000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>2861700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>942600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5218500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>1798800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>1795900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>2869400</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2170,57 +2259,63 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>15362000</v>
+      </c>
+      <c r="E43" s="3">
         <v>14369000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>11958000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>10416900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>9960200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>8160100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>7507300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6497100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5422500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4509200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3987700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3537500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3310700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3293100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3125800</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2248,8 +2343,8 @@
       <c r="K44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2266,39 +2361,42 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>5488000</v>
+        <v>4753000</v>
       </c>
       <c r="E45" s="3">
+        <v>5359000</v>
+      </c>
+      <c r="F45" s="3">
         <v>5609000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6163300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>5173000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4252400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3593100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2926200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2398400</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2309,44 +2407,47 @@
         <v>0</v>
       </c>
       <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3">
         <v>66300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>69800</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>20975000</v>
+        <v>30455000</v>
       </c>
       <c r="E46" s="3">
+        <v>20846000</v>
+      </c>
+      <c r="F46" s="3">
         <v>19707000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>19958300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>16735500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>18075600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>13753100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>11603900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>11168900</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2362,153 +2463,165 @@
       <c r="Q46" s="3">
         <v>0</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>87368000</v>
+      </c>
+      <c r="E47" s="3">
         <v>79635000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>64209000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>50686600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>50571500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>42311800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>37455500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>31771500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>24405300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>23482600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>20937300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>19018000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>18054700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>16475500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>15963000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>982000</v>
+      </c>
+      <c r="E48" s="3">
         <v>983000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1054000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1164500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1309900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1271500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1401900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1131700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1119600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1177100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1037200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1921200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>960900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>933700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>911300</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2189000</v>
+        <v>2044000</v>
       </c>
       <c r="E49" s="3">
+        <v>1961000</v>
+      </c>
+      <c r="F49" s="3">
         <v>1915000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1772300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1925600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1861300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1737500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1698900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1599800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>882200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>942500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>12900</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P49" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2554,9 +2667,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2602,42 +2718,45 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>846000</v>
+        <v>1404000</v>
       </c>
       <c r="E52" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="F52" s="3">
         <v>742000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>646200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>525800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>540900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>547300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>325800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>407600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14900</v>
       </c>
-      <c r="M52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
@@ -2650,9 +2769,12 @@
       <c r="Q52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2698,57 +2820,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>123039000</v>
+      </c>
+      <c r="E54" s="3">
         <v>105745000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>88691000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>75465000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>71132300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>64098300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>54910500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>46575000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>38701200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>33427500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>29819300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>25787600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>24408200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>22694700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>21844800</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2767,8 +2895,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2787,61 +2916,65 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>49181000</v>
+        <v>52135000</v>
       </c>
       <c r="E57" s="3">
+        <v>46303000</v>
+      </c>
+      <c r="F57" s="3">
         <v>40902000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>35881200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31907400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24779600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>22283800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18956700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15889000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2495500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2067800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1893800</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P57" s="3" t="s">
         <v>8</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>81000</v>
+        <v>90000</v>
       </c>
       <c r="E58" s="3">
         <v>0</v>
@@ -2865,104 +2998,110 @@
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>25000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>27200</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>23884000</v>
+        <v>33278000</v>
       </c>
       <c r="E59" s="3">
+        <v>26637000</v>
+      </c>
+      <c r="F59" s="3">
         <v>20446000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17304500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15615800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>16295500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13988200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>12171200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9582400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7863700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7141000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>5844200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7849700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6786200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6350200</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>73146000</v>
+        <v>85503000</v>
       </c>
       <c r="E60" s="3">
+        <v>72940000</v>
+      </c>
+      <c r="F60" s="3">
         <v>61348000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>53185700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>47523200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>41075100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>36272000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>31127900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>25471400</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2978,105 +3117,114 @@
       <c r="Q60" s="3">
         <v>0</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7008000</v>
+        <v>7012000</v>
       </c>
       <c r="E61" s="3">
+        <v>7089000</v>
+      </c>
+      <c r="F61" s="3">
         <v>7066000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>6388300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5079700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5575100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4608600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4404900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3306300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3123200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2680700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2164700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1860900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2063100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2442100</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>8</v>
+      <c r="D62" s="3">
+        <v>200000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>125000</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H62" s="3">
         <v>143400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>95500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5900</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M62" s="3">
         <v>111300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>109300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>98900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>28400</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3122,9 +3270,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3170,9 +3321,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3218,57 +3372,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>92716000</v>
+      </c>
+      <c r="E66" s="3">
         <v>80154000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>68414000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>59574000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>52900700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>47059700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>41011700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>35538700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>28912700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>25470400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>22529900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>18859000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>18218700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>16687700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>16038100</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3287,8 +3447,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3334,9 +3495,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3382,9 +3546,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3392,10 +3559,10 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
+        <v>0</v>
+      </c>
+      <c r="F70" s="3">
         <v>494000</v>
-      </c>
-      <c r="F70" s="3">
-        <v>493900</v>
       </c>
       <c r="G70" s="3">
         <v>493900</v>
@@ -3410,7 +3577,7 @@
         <v>493900</v>
       </c>
       <c r="K70" s="3">
-        <v>0</v>
+        <v>493900</v>
       </c>
       <c r="L70" s="3">
         <v>0</v>
@@ -3430,9 +3597,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3478,57 +3648,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27327000</v>
+      </c>
+      <c r="E72" s="3">
         <v>24283000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>18801000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>15721200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>15339700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>13354900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10679600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8386600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6031700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5140400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>4686600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>4133400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3500000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3454400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3495000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3574,9 +3750,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3622,9 +3801,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3670,57 +3852,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>30323000</v>
+      </c>
+      <c r="E76" s="3">
         <v>25591000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>19783000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>15397100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17737700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>16544700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>13179300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>10327900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>9284800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7957100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7289400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6928600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6189500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>6007000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5806700</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3766,110 +3954,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>11308000</v>
+      </c>
+      <c r="E81" s="3">
         <v>8480000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3903000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>722000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3350900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>5704600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3970300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2615300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1592200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1031000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1267600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1281000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1165400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>902300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1015500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3888,56 +4085,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>313000</v>
+      </c>
+      <c r="E83" s="3">
         <v>284000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>285000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>306000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>279700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>274900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>239800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>190400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>169900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>199500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>150500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>97100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>101300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>94400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>88500</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3983,9 +4184,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4031,9 +4235,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4079,9 +4286,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4127,9 +4337,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4175,57 +4388,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17548000</v>
+      </c>
+      <c r="E89" s="3">
         <v>15119000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>10643000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>6849000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>7761700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>6905600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6261600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6284800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>3756800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>2732700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2292900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1725600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1899900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1691400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1497900</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4244,56 +4463,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-348000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-285000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-252000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-292000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-243500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-223500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-363500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-266000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-155700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-215000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-130700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-108100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-140400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-127700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-78900</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4339,9 +4562,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4387,57 +4613,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14527000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13749000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10842000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7956000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-3119800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-6117700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-4338300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7034900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3406700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2480700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1923900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-836900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1356500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-264900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-744900</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4456,56 +4688,60 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2871000</v>
+      </c>
+      <c r="E96" s="3">
         <v>674000</v>
-      </c>
-      <c r="E96" s="3">
-        <v>234000</v>
       </c>
       <c r="F96" s="3">
         <v>234000</v>
       </c>
       <c r="G96" s="3">
+        <v>234000</v>
+      </c>
+      <c r="H96" s="3">
         <v>3746500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1551000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1643200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>654900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>395400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-519000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-403600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-892600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-175600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-853700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-263600</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4551,9 +4787,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4599,9 +4838,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4647,57 +4889,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3037000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1316000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>78000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1126000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4516300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-938800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1770900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>549800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-300900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-250400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-252800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-855400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-646800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1404100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-755700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4722,76 +4970,82 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L101" s="3">
         <v>-300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-200</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>-600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-500</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="E102" s="3">
         <v>54000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-121000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>19000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>125600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-150900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>152400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-200300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>48900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>116000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>33300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-104000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-3200</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
